--- a/api/clv3/xlsx/en/LocationType-category.xlsx
+++ b/api/clv3/xlsx/en/LocationType-category.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
   </si>
   <si>
     <t>A</t>
@@ -420,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -442,104 +445,107 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv3/xlsx/en/LocationType-category.xlsx
+++ b/api/clv3/xlsx/en/LocationType-category.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>code</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>public-database</t>
   </si>
   <si>
     <t>A</t>
@@ -423,10 +420,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,107 +442,104 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv3/xlsx/en/LocationType-category.xlsx
+++ b/api/clv3/xlsx/en/LocationType-category.xlsx
@@ -14,21 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>code</t>
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>url</t>
   </si>
   <si>
     <t>status</t>
@@ -420,10 +411,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,113 +424,104 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
